--- a/UPZ.xlsx
+++ b/UPZ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcjua\Desktop\Defunciones_EISP_SDS_2026\Tablas_Referencia_EEVV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saludcapitalgovco-my.sharepoint.com/personal/jcleon_saludcapital_gov_co/Documents/Tablas_Referencia_SDS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDE0EC5-269A-47C5-958B-55DDE789F5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{BEDE0EC5-269A-47C5-958B-55DDE789F5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C823CC87-8086-4350-ABDF-0DC7D82FF0E9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2D30E513-7EC1-4288-900C-D640885E60A1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="155">
   <si>
     <t>codUPZ</t>
   </si>
@@ -495,6 +495,15 @@
   </si>
   <si>
     <t>SUR OCCIDENTE</t>
+  </si>
+  <si>
+    <t>SUMAPAZ - RURAL SUMAPAZ</t>
+  </si>
+  <si>
+    <t>UPR ZONA NORTE</t>
+  </si>
+  <si>
+    <t>UPR RIO TUNJUELO</t>
   </si>
 </sst>
 </file>
@@ -530,13 +539,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -866,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16BB3412-3BBE-4CD6-B818-B262BD261DBA}">
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -3069,8 +3090,62 @@
         <v>150</v>
       </c>
     </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>920</v>
+      </c>
+      <c r="B130" t="s">
+        <v>152</v>
+      </c>
+      <c r="C130">
+        <v>20</v>
+      </c>
+      <c r="D130" t="s">
+        <v>133</v>
+      </c>
+      <c r="E130" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C131" s="1">
+        <v>11</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E131" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>1003</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C132" s="1">
+        <v>19</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E132" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E129" xr:uid="{16BB3412-3BBE-4CD6-B818-B262BD261DBA}"/>
+  <conditionalFormatting sqref="A130:A132">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>